--- a/data/trans_dic/IP16B02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,84; 100,0</t>
+          <t>83,7; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,01; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,25; 100,0</t>
+          <t>74,34; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,58; 100,0</t>
+          <t>76,71; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,74; 98,0</t>
+          <t>85,29; 98,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,44; 100,0</t>
+          <t>86,87; 100,0</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,08; 91,77</t>
+          <t>55,38; 89,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,59; 88,54</t>
+          <t>56,62; 88,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,16; 90,11</t>
+          <t>59,31; 89,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,87; 100,0</t>
+          <t>82,59; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,35; 90,14</t>
+          <t>62,83; 89,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,28; 100,0</t>
+          <t>83,82; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,91; 94,07</t>
+          <t>76,81; 93,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,63; 86,05</t>
+          <t>66,65; 86,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,02; 93,12</t>
+          <t>74,77; 93,21</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,48; 92,16</t>
+          <t>57,83; 92,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,19; 100,0</t>
+          <t>74,2; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,9; 100,0</t>
+          <t>69,22; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,17; 95,97</t>
+          <t>62,72; 95,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,73; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,57; 93,2</t>
+          <t>72,16; 93,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,16; 95,24</t>
+          <t>73,81; 95,34</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,9; 84,2</t>
+          <t>40,62; 83,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,71; 84,1</t>
+          <t>47,66; 84,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,61; 89,32</t>
+          <t>55,38; 88,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,49; 82,78</t>
+          <t>42,92; 82,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,82; 100,0</t>
+          <t>72,55; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,29; 100,0</t>
+          <t>60,76; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,7; 78,44</t>
+          <t>49,76; 79,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,01; 89,04</t>
+          <t>64,07; 88,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,95; 90,89</t>
+          <t>64,38; 90,37</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,76; 88,59</t>
+          <t>67,27; 88,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,43</t>
+          <t>72,48; 87,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,84; 90,06</t>
+          <t>73,71; 90,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,33; 94,24</t>
+          <t>80,01; 94,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,6; 92,79</t>
+          <t>79,87; 93,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,35; 96,15</t>
+          <t>83,34; 95,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 90,46</t>
+          <t>79,44; 90,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,77; 88,87</t>
+          <t>79,11; 88,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,04; 91,57</t>
+          <t>80,82; 91,34</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7266</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23571</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9485</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18595</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10625</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19288</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>42166</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20110</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20815; 24868</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14931; 20083</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8651; 11277</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>38338; 44064</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18035; 20762</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10680</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15105</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21630</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22697</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14693</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32310</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>37801</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>31159</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7917; 12770</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11286; 17563</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12563; 18950</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18866; 22843</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17919; 25602</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12762; 15225</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28526; 34782</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>32293; 41892</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>27219; 33934</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6703</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13315</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11984</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8489</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12092</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13181</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>25408</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>25165</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9682; 15445</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9465; 12756</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9322; 13467</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9987; 15176</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>21799; 28224</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>21166; 27341</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7973</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11689</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13678</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11855</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17978</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>23544</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5014; 10247</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8182; 14431</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10274; 16356</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6598; 12706</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9070; 12502</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5623; 9255</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13791; 21938</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>19008; 26368</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17902; 25131</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>32622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63680</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52148</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84770</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>128920</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>98649</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27316; 36076</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57051; 68588</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45684; 55848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46984; 55411</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>59559; 69537</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>43068; 49505</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>78912; 89573</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>121270; 136264</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>91854; 103806</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Edad-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,7; 100,0</t>
+          <t>81,74; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,34; 100,0</t>
+          <t>76,92; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,71; 100,0</t>
+          <t>70,16; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,29; 98,03</t>
+          <t>86,24; 98,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,87; 100,0</t>
+          <t>84,63; 100,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,38; 89,34</t>
+          <t>54,03; 90,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,62; 88,11</t>
+          <t>56,86; 88,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,31; 89,47</t>
+          <t>59,66; 90,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,59; 100,0</t>
+          <t>80,95; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,83; 89,77</t>
+          <t>64,75; 90,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,82; 100,0</t>
+          <t>85,27; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,81; 93,66</t>
+          <t>76,18; 93,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,65; 86,46</t>
+          <t>66,34; 86,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,77; 93,21</t>
+          <t>73,8; 93,2</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,83; 92,25</t>
+          <t>60,56; 92,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,2; 100,0</t>
+          <t>67,46; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,22; 100,0</t>
+          <t>68,28; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,72; 95,32</t>
+          <t>61,61; 95,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,16; 93,43</t>
+          <t>70,02; 93,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73,81; 95,34</t>
+          <t>75,94; 95,86</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,62; 83,02</t>
+          <t>42,21; 84,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,66; 84,06</t>
+          <t>45,6; 83,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,38; 88,16</t>
+          <t>54,01; 87,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,92; 82,67</t>
+          <t>43,91; 82,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,55; 100,0</t>
+          <t>74,48; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,76; 100,0</t>
+          <t>67,68; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,76; 79,16</t>
+          <t>49,22; 78,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,07; 88,87</t>
+          <t>66,29; 89,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,38; 90,37</t>
+          <t>64,26; 90,57</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,27; 88,84</t>
+          <t>68,48; 88,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,48; 87,14</t>
+          <t>72,72; 87,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 90,11</t>
+          <t>74,2; 89,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,01; 94,36</t>
+          <t>82,08; 94,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,87; 93,25</t>
+          <t>79,63; 93,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,79</t>
+          <t>82,2; 96,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,44; 90,18</t>
+          <t>78,57; 90,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,11; 88,9</t>
+          <t>78,87; 88,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,82; 91,34</t>
+          <t>80,87; 91,38</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20815; 24868</t>
+          <t>20327; 24868</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14931; 20083</t>
+          <t>15447; 20083</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8651; 11277</t>
+          <t>7912; 11277</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38338; 44064</t>
+          <t>38766; 44273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18035; 20762</t>
+          <t>17571; 20762</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7917; 12770</t>
+          <t>7724; 12953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11286; 17563</t>
+          <t>11334; 17664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12563; 18950</t>
+          <t>12637; 19086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18866; 22843</t>
+          <t>18492; 22843</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17919; 25602</t>
+          <t>18467; 25825</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12762; 15225</t>
+          <t>12982; 15225</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28526; 34782</t>
+          <t>28290; 34898</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32293; 41892</t>
+          <t>32145; 41716</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27219; 33934</t>
+          <t>26869; 33929</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9682; 15445</t>
+          <t>10139; 15441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9465; 12756</t>
+          <t>8605; 12756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9322; 13467</t>
+          <t>9195; 13467</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9987; 15176</t>
+          <t>9809; 15242</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21799; 28224</t>
+          <t>21153; 28234</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21166; 27341</t>
+          <t>21778; 27491</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5014; 10247</t>
+          <t>5210; 10429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8182; 14431</t>
+          <t>7829; 14373</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10274; 16356</t>
+          <t>10020; 16281</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6598; 12706</t>
+          <t>6750; 12716</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9070; 12502</t>
+          <t>9311; 12502</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5623; 9255</t>
+          <t>6264; 9255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13791; 21938</t>
+          <t>13642; 21760</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19008; 26368</t>
+          <t>19669; 26437</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17902; 25131</t>
+          <t>17870; 25186</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27316; 36076</t>
+          <t>27806; 36010</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57051; 68588</t>
+          <t>57235; 68961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45684; 55848</t>
+          <t>45988; 55696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46984; 55411</t>
+          <t>48201; 55538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59559; 69537</t>
+          <t>59379; 69492</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43068; 49505</t>
+          <t>42480; 49702</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78912; 89573</t>
+          <t>78049; 89912</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121270; 136264</t>
+          <t>120894; 135732</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>91854; 103806</t>
+          <t>91907; 103862</t>
         </is>
       </c>
     </row>
